--- a/docs/培训/OpenWorker培训/02-交期风险/订单清单.xlsx
+++ b/docs/培训/OpenWorker培训/02-交期风险/订单清单.xlsx
@@ -505,10 +505,10 @@
         <v>6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -541,10 +541,10 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46249</v>
+        <v>46254</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46300</v>
+        <v>46305</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -613,10 +613,10 @@
         <v>8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -649,10 +649,10 @@
         <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         <v>3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46266</v>
+        <v>46271</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46315</v>
+        <v>46320</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -757,10 +757,10 @@
         <v>6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46324</v>
+        <v>46329</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         <v>12</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46339</v>
+        <v>46344</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46279</v>
+        <v>46284</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46354</v>
+        <v>46359</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         <v>5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46224</v>
+        <v>46229</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
         <v>4</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
